--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -4344,7 +4344,7 @@
         <v>117538006</v>
       </c>
       <c r="B30" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>117538012</v>
       </c>
       <c r="B31" t="n">
-        <v>57306</v>
+        <v>57307</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>117577625</v>
       </c>
       <c r="B32" t="n">
-        <v>103338</v>
+        <v>103340</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -4734,10 +4734,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118361638</v>
+        <v>118361643</v>
       </c>
       <c r="B33" t="n">
-        <v>44526</v>
+        <v>44525</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4750,26 +4750,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102019</v>
+        <v>102018</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4872,10 +4872,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118361643</v>
+        <v>118361638</v>
       </c>
       <c r="B34" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4888,26 +4888,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102018</v>
+        <v>102019</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -4734,10 +4734,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118361643</v>
+        <v>118361638</v>
       </c>
       <c r="B33" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4750,26 +4750,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102018</v>
+        <v>102019</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4872,10 +4872,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118361638</v>
+        <v>118361643</v>
       </c>
       <c r="B34" t="n">
-        <v>44526</v>
+        <v>44525</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4888,26 +4888,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102019</v>
+        <v>102018</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4341,10 +4341,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117538006</v>
+        <v>117538012</v>
       </c>
       <c r="B30" t="n">
-        <v>57304</v>
+        <v>57307</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4353,25 +4353,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4387,7 +4387,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117538012</v>
+        <v>117577625</v>
       </c>
       <c r="B31" t="n">
-        <v>57307</v>
+        <v>103340</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102977</v>
+        <v>222412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4511,17 +4511,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4563,22 +4559,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4587,6 +4583,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4602,411 +4599,6 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>117577625</v>
-      </c>
-      <c r="B32" t="n">
-        <v>103340</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>"Tegelbacken", Sm</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>578587</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6410741</v>
-      </c>
-      <c r="S32" t="n">
-        <v>100</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Hallingeberg</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Sven Halling</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Sven Halling</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>118361643</v>
-      </c>
-      <c r="B33" t="n">
-        <v>44525</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>102018</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Bredbrämad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Zygaena lonicerae</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Scheven, 1777)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>"Tegelbacken", Sm</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>578587</v>
-      </c>
-      <c r="R33" t="n">
-        <v>6410741</v>
-      </c>
-      <c r="S33" t="n">
-        <v>100</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Hallingeberg</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Sven Halling</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Sven Halling</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>118361638</v>
-      </c>
-      <c r="B34" t="n">
-        <v>44526</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>102019</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Klubbsprötad bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Zygaena minos</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>"Tegelbacken", Sm</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>578587</v>
-      </c>
-      <c r="R34" t="n">
-        <v>6410741</v>
-      </c>
-      <c r="S34" t="n">
-        <v>100</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Hallingeberg</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Sven Halling</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Sven Halling</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -4605,7 +4605,7 @@
         <v>124654936</v>
       </c>
       <c r="B32" t="n">
-        <v>57429</v>
+        <v>57582</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4732,6 +4732,125 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126246654</v>
+      </c>
+      <c r="B33" t="n">
+        <v>56608</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>"Tegelbacken", Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>578587</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6410741</v>
+      </c>
+      <c r="S33" t="n">
+        <v>100</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sven Halling, Ann Newsome</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -4737,7 +4737,7 @@
         <v>126246654</v>
       </c>
       <c r="B33" t="n">
-        <v>56608</v>
+        <v>56612</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4737,7 +4737,7 @@
         <v>126246654</v>
       </c>
       <c r="B33" t="n">
-        <v>56612</v>
+        <v>56613</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4850,6 +4850,134 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126301886</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98346</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>"Tegelbacken", Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>578587</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6410741</v>
+      </c>
+      <c r="S34" t="n">
+        <v>100</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sven Halling, Ann Newsome</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4979,6 +4979,133 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134425748</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>"Tegelbacken", Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>578587</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6410741</v>
+      </c>
+      <c r="S35" t="n">
+        <v>100</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,68 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16868432</v>
+        <v>111595525</v>
       </c>
       <c r="B2" t="n">
-        <v>101257</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>707</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandnäva</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geranium lanuginosum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Lam.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>"Tegelbacken", Sm</t>
+          <t>Svensgöl, Hult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578586.8882896412</v>
+        <v>578725</v>
       </c>
       <c r="R2" t="n">
-        <v>6410740.950670342</v>
+        <v>6410706</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,22 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal asplåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,75 +770,84 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16872227</v>
+        <v>110245711</v>
       </c>
       <c r="B3" t="n">
-        <v>96309</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219797</v>
+        <v>706</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R3" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -879,22 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-07-30</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-07-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +888,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -914,51 +900,54 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16878306</v>
+        <v>16868432</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104171</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>707</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brandnäva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Geranium lanuginosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Lam.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -968,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R4" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -998,22 +987,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-06-01</t>
+          <t>2014-07-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-06-01</t>
+          <t>2014-07-04</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,37 +1029,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>60888319</v>
+        <v>95858887</v>
       </c>
       <c r="B5" t="n">
-        <v>42504</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101070</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1080,35 +1064,25 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R5" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1135,22 +1109,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-08-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-08-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,6 +1123,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1170,22 +1135,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sven Halling, Magnus Kasselstrand</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>65252232</v>
+        <v>79602120</v>
       </c>
       <c r="B6" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,16 +1153,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1223,7 +1183,12 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1232,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R6" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1262,22 +1227,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-05-01</t>
+          <t>2019-08-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-05-01</t>
+          <t>2019-08-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,65 +1262,55 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66835725</v>
+        <v>102933581</v>
       </c>
       <c r="B7" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102018</v>
+        <v>100038</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1369,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R7" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1399,22 +1354,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1441,67 +1386,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66835754</v>
+        <v>65252232</v>
       </c>
       <c r="B8" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1510,10 +1436,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R8" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1540,22 +1466,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1582,58 +1508,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>72119920</v>
+        <v>124654936</v>
       </c>
       <c r="B9" t="n">
-        <v>44332</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102020</v>
+        <v>100067</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1647,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R9" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1677,22 +1593,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1701,7 +1617,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1713,44 +1628,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72119955</v>
+        <v>95909593</v>
       </c>
       <c r="B10" t="n">
-        <v>44331</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102019</v>
+        <v>100082</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1758,14 +1668,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1785,10 +1690,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R10" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
@@ -1815,22 +1720,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1839,7 +1734,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1858,15 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>78041334</v>
+        <v>79861625</v>
       </c>
       <c r="B11" t="n">
-        <v>55649</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1874,31 +1763,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208255</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1909,7 +1793,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1923,10 +1807,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R11" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -1953,22 +1837,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2019-09-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2019-09-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1977,7 +1861,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1989,22 +1872,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79602120</v>
+        <v>60888319</v>
       </c>
       <c r="B12" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,16 +1890,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100001</v>
+        <v>101070</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2034,9 +1912,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -2056,10 +1939,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R12" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -2086,22 +1969,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-08-25</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2016-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-08-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:45</t>
+          <t>2016-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2121,22 +1994,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95858892</v>
+        <v>66835725</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2144,39 +2012,44 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102018</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2188,10 +2061,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R13" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -2218,22 +2091,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2242,7 +2105,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2254,44 +2116,39 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95858887</v>
+        <v>72119955</v>
       </c>
       <c r="B14" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45045</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>102019</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2301,25 +2158,35 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R14" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2346,22 +2213,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2389,42 +2256,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96043204</v>
+        <v>72119920</v>
       </c>
       <c r="B15" t="n">
-        <v>55392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208257</v>
+        <v>102020</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2434,13 +2296,13 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2454,10 +2316,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R15" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2484,22 +2346,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-11</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-11</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2520,72 +2382,84 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Ann Newsome, Sven Halling</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96507995</v>
+        <v>66835754</v>
       </c>
       <c r="B16" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>102021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578628.3717956286</v>
+        <v>578587</v>
       </c>
       <c r="R16" t="n">
-        <v>6410775.315829419</v>
+        <v>6410741</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2609,22 +2483,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2633,84 +2497,86 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96507964</v>
+        <v>110917207</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>102626</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578688.8416607701</v>
+        <v>578587</v>
       </c>
       <c r="R17" t="n">
-        <v>6410712.054651793</v>
+        <v>6410741</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2734,22 +2600,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2758,34 +2614,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>102425823</v>
+        <v>117538012</v>
       </c>
       <c r="B18" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2793,49 +2643,57 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>102977</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578633.3495778691</v>
+        <v>578587</v>
       </c>
       <c r="R18" t="n">
-        <v>6410766.359068997</v>
+        <v>6410741</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,22 +2717,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,84 +2741,86 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Larsgunnar Nilsson</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>102425918</v>
+        <v>79139661</v>
       </c>
       <c r="B19" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221946</v>
+        <v>102990</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>578696.9210446723</v>
+        <v>578587</v>
       </c>
       <c r="R19" t="n">
-        <v>6410789.972517342</v>
+        <v>6410741</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2984,22 +2844,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3008,74 +2858,68 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Larsgunnar Nilsson, Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>102874378</v>
+        <v>117136615</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103012</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3083,17 +2927,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>S 100 metersberget, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>578753.8157100691</v>
+        <v>578587</v>
       </c>
       <c r="R20" t="n">
-        <v>6410745.816195717</v>
+        <v>6410741</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3117,27 +2961,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2 blommande plantor av knärot 1.5 meter skilda samt 17 bladrosetter.</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3146,7 +2985,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3165,73 +3003,63 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>102874540</v>
+        <v>65686154</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>SSV 100 metersberget, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>578694.8569467356</v>
+        <v>578587</v>
       </c>
       <c r="R21" t="n">
-        <v>6410731.87879331</v>
+        <v>6410741</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3255,22 +3083,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2017-05-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
+          <t>2017-05-20</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3279,7 +3107,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3298,15 +3125,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104981065</v>
+        <v>134425748</v>
       </c>
       <c r="B22" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58698</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3314,46 +3136,54 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>103055</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>A 58458, Hult, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>578669.7968211162</v>
+        <v>578587</v>
       </c>
       <c r="R22" t="n">
-        <v>6410730.85554819</v>
+        <v>6410741</v>
       </c>
       <c r="S22" t="n">
         <v>100</v>
@@ -3380,22 +3210,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-12-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-12-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3410,27 +3240,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110245711</v>
+        <v>56021390</v>
       </c>
       <c r="B23" t="n">
-        <v>101246</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43219</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,39 +3263,44 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>706</v>
+        <v>201028</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3482,10 +3312,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R23" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S23" t="n">
         <v>100</v>
@@ -3512,22 +3342,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3536,7 +3356,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3548,62 +3367,62 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110386784</v>
+        <v>55919018</v>
       </c>
       <c r="B24" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219875</v>
+        <v>201075</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3615,10 +3434,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>578586.8882896412</v>
+        <v>578587</v>
       </c>
       <c r="R24" t="n">
-        <v>6410740.950670342</v>
+        <v>6410741</v>
       </c>
       <c r="S24" t="n">
         <v>100</v>
@@ -3645,22 +3464,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-05-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3669,7 +3478,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3688,15 +3496,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111595525</v>
+        <v>72232452</v>
       </c>
       <c r="B25" t="n">
-        <v>90151</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43258</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3704,48 +3507,66 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>366</v>
+        <v>201129</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>578725.2392689644</v>
+        <v>578587</v>
       </c>
       <c r="R25" t="n">
-        <v>6410706.376212179</v>
+        <v>6410741</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3769,27 +3590,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal asplåga</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3805,27 +3621,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111595483</v>
+        <v>60747030</v>
       </c>
       <c r="B26" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43309</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3833,53 +3644,62 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>201146</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>578724.2708698318</v>
+        <v>578587</v>
       </c>
       <c r="R26" t="n">
-        <v>6410783.051849495</v>
+        <v>6410741</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3903,27 +3723,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2016-07-27</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2016-07-27</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>6 blommor</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3932,34 +3747,28 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117136607</v>
+        <v>78041334</v>
       </c>
       <c r="B27" t="n">
-        <v>57808</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3967,26 +3776,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102990</v>
+        <v>208255</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3997,7 +3811,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4041,22 +3855,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2019-05-23</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2019-05-23</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4065,6 +3879,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4083,42 +3898,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117136615</v>
+        <v>96043204</v>
       </c>
       <c r="B28" t="n">
-        <v>57521</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56876</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103012</v>
+        <v>208257</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4129,7 +3944,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4173,22 +3988,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2021-09-11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2021-09-11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4197,6 +4002,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4208,22 +4014,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117246856</v>
+        <v>126246654</v>
       </c>
       <c r="B29" t="n">
-        <v>57382</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4231,26 +4032,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102626</v>
+        <v>208260</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4258,16 +4064,8 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4309,12 +4107,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4323,6 +4121,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4334,22 +4133,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117538012</v>
+        <v>16872227</v>
       </c>
       <c r="B30" t="n">
-        <v>57307</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4357,44 +4151,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102977</v>
+        <v>219797</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>"Tegelbacken", Sm</t>
@@ -4431,22 +4212,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2009-07-30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>2009-07-30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4473,15 +4244,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117577625</v>
+        <v>126301886</v>
       </c>
       <c r="B31" t="n">
-        <v>103340</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4489,34 +4255,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222412</v>
+        <v>219799</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
@@ -4559,17 +4329,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -4595,62 +4365,57 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124654936</v>
+        <v>110386784</v>
       </c>
       <c r="B32" t="n">
-        <v>57582</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100067</v>
+        <v>219875</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4692,22 +4457,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4716,6 +4471,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4734,51 +4490,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126246654</v>
+        <v>95858892</v>
       </c>
       <c r="B33" t="n">
-        <v>56613</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>208260</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4820,12 +4575,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4853,68 +4608,56 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126301886</v>
+        <v>96507865</v>
       </c>
       <c r="B34" t="n">
-        <v>98346</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219799</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>"Tegelbacken", Sm</t>
+          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578587</v>
+        <v>578722</v>
       </c>
       <c r="R34" t="n">
-        <v>6410741</v>
+        <v>6410806</v>
       </c>
       <c r="S34" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4938,22 +4681,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4969,80 +4702,72 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134425748</v>
+        <v>96507964</v>
       </c>
       <c r="B35" t="n">
-        <v>58698</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103055</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>"Tegelbacken", Sm</t>
+          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578587</v>
+        <v>578689</v>
       </c>
       <c r="R35" t="n">
-        <v>6410741</v>
+        <v>6410712</v>
       </c>
       <c r="S35" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5066,22 +4791,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5090,21 +4805,1290 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>102874367</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>S 100 metersberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>578754</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6410746</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
           <t>Sven Halling</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
+      <c r="AX36" t="inlineStr">
         <is>
           <t>Sven Halling</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>102874540</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SSV 100 metersberget, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>578695</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6410732</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>111595448</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svensgöl, Hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>578729</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6410799</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>111595465</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svensgöl, Hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>578746</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6410805</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111595483</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svensgöl, Hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>578724</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6410783</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>6 blommor</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>96507995</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>578628</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6410775</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>102425823</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svensgöl, Hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>578633</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6410766</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2022-07-22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2022-07-22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>96507688</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>578691</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6410795</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2021-10-06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>102425918</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Svensgöl, Hult, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>578697</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6410790</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2022-07-22</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2022-07-22</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Larsgunnar Nilsson, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>117577625</v>
+      </c>
+      <c r="B45" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>"Tegelbacken", Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>578587</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6410741</v>
+      </c>
+      <c r="S45" t="n">
+        <v>100</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>16878306</v>
+      </c>
+      <c r="B46" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>"Tegelbacken", Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>578587</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6410741</v>
+      </c>
+      <c r="S46" t="n">
+        <v>100</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58458-2022 artfynd.xlsx
+++ b/artfynd/A 58458-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>65252232</v>
+        <v>136349435</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>56958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,16 +1432,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100045</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1462,7 +1462,12 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1501,22 +1506,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-05-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-05-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,16 +1547,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65252232</t>
+          <t>https://artportalen.se/Sighting/136349435</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124654936</v>
+        <v>65252232</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,16 +1564,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1589,12 +1594,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1633,22 +1633,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1674,16 +1674,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124654936</t>
+          <t>https://artportalen.se/Sighting/65252232</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95909593</v>
+        <v>124654936</v>
       </c>
       <c r="B10" t="n">
-        <v>57890</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100082</v>
+        <v>100067</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1721,7 +1721,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1765,12 +1765,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-04</t>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-04</t>
+          <t>2025-05-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,22 +1800,22 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95909593</t>
+          <t>https://artportalen.se/Sighting/124654936</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79861625</v>
+        <v>95909593</v>
       </c>
       <c r="B11" t="n">
-        <v>57141</v>
+        <v>57890</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,21 +1823,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100082</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1843,7 +1853,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1887,22 +1897,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2019-09-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2019-09-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2021-09-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1928,38 +1928,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79861625</t>
+          <t>https://artportalen.se/Sighting/95909593</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>60888319</v>
+        <v>79861625</v>
       </c>
       <c r="B12" t="n">
-        <v>43212</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101070</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silversmygare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hesperia comma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1967,20 +1967,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2024,12 +2019,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-08-07</t>
+          <t>2019-09-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-08-07</t>
+          <t>2019-09-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2049,49 +2054,49 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sven Halling, Magnus Kasselstrand</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60888319</t>
+          <t>https://artportalen.se/Sighting/79861625</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66835725</v>
+        <v>60888319</v>
       </c>
       <c r="B13" t="n">
-        <v>45044</v>
+        <v>43212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102018</v>
+        <v>101070</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Silversmygare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Hesperia comma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2151,12 +2156,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2016-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2016-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2176,49 +2181,49 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66835725</t>
+          <t>https://artportalen.se/Sighting/60888319</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>72119955</v>
+        <v>66835725</v>
       </c>
       <c r="B14" t="n">
-        <v>45045</v>
+        <v>45044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102019</v>
+        <v>102018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2278,22 +2283,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:10</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2302,7 +2297,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2314,49 +2308,49 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72119955</t>
+          <t>https://artportalen.se/Sighting/66835725</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>72119920</v>
+        <v>72119955</v>
       </c>
       <c r="B15" t="n">
-        <v>45046</v>
+        <v>45045</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102020</v>
+        <v>102019</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalsprötad bastardsvärmare</t>
+          <t>Klubbsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Zygaena osterodensis</t>
+          <t>Zygaena minos</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Reiss, 1921</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2452,22 +2446,22 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ann Newsome, Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72119920</t>
+          <t>https://artportalen.se/Sighting/72119955</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66835754</v>
+        <v>72119920</v>
       </c>
       <c r="B16" t="n">
-        <v>45049</v>
+        <v>45046</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,26 +2469,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102021</v>
+        <v>102020</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Smalsprötad bastardsvärmare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Zygaena osterodensis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Reiss, 1921</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2507,14 +2501,10 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2558,12 +2548,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2018-07-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2572,6 +2572,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2583,60 +2584,69 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Ann Newsome, Sven Halling</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/66835754</t>
+          <t>https://artportalen.se/Sighting/72119920</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110917207</v>
+        <v>66835754</v>
       </c>
       <c r="B17" t="n">
-        <v>58039</v>
+        <v>45049</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102626</v>
+        <v>102021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>parning/parningsceremonier</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2680,12 +2690,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2711,16 +2721,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110917207</t>
+          <t>https://artportalen.se/Sighting/66835754</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117538012</v>
+        <v>110917207</v>
       </c>
       <c r="B18" t="n">
-        <v>57947</v>
+        <v>58039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2728,16 +2738,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102977</v>
+        <v>102626</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2758,7 +2768,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2802,22 +2812,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>2023-07-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2843,38 +2843,38 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117538012</t>
+          <t>https://artportalen.se/Sighting/110917207</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>79139661</v>
+        <v>117538012</v>
       </c>
       <c r="B19" t="n">
-        <v>58497</v>
+        <v>57947</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102990</v>
+        <v>102977</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2890,7 +2890,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2934,12 +2934,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2019-07-22</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2019-07-22</t>
+          <t>2024-06-03</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2959,22 +2969,22 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79139661</t>
+          <t>https://artportalen.se/Sighting/117538012</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117136615</v>
+        <v>79139661</v>
       </c>
       <c r="B20" t="n">
-        <v>58238</v>
+        <v>58497</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2982,21 +2992,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103012</v>
+        <v>102990</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3012,7 +3022,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3056,22 +3066,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3091,44 +3091,44 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117136615</t>
+          <t>https://artportalen.se/Sighting/79139661</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>65686154</v>
+        <v>117136615</v>
       </c>
       <c r="B21" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3147,6 +3147,11 @@
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>"Tegelbacken", Sm</t>
@@ -3183,22 +3188,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2017-05-20</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2017-05-20</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3224,38 +3229,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/65686154</t>
+          <t>https://artportalen.se/Sighting/117136615</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134425748</v>
+        <v>65686154</v>
       </c>
       <c r="B22" t="n">
-        <v>58698</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3274,11 +3279,6 @@
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>"Tegelbacken", Sm</t>
@@ -3315,22 +3315,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2017-05-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2017-05-20</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3356,59 +3356,54 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134425748</t>
+          <t>https://artportalen.se/Sighting/65686154</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>56021390</v>
+        <v>136349431</v>
       </c>
       <c r="B23" t="n">
-        <v>43219</v>
+        <v>58263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>201028</v>
+        <v>103019</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3452,12 +3447,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2015-08-04</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2015-08-04</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3483,38 +3488,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56021390</t>
+          <t>https://artportalen.se/Sighting/136349431</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>55919018</v>
+        <v>134425748</v>
       </c>
       <c r="B24" t="n">
-        <v>43378</v>
+        <v>58698</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>201075</v>
+        <v>103055</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3522,20 +3527,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3579,12 +3579,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2015-05-26</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2015-05-26</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3610,16 +3620,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55919018</t>
+          <t>https://artportalen.se/Sighting/134425748</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>72232452</v>
+        <v>56021390</v>
       </c>
       <c r="B25" t="n">
-        <v>43258</v>
+        <v>43219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3627,26 +3637,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>201129</v>
+        <v>201028</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3659,11 +3669,7 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3710,22 +3716,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2018-07-10</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2015-08-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3734,7 +3730,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3752,16 +3747,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72232452</t>
+          <t>https://artportalen.se/Sighting/56021390</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>60747030</v>
+        <v>55919018</v>
       </c>
       <c r="B26" t="n">
-        <v>43309</v>
+        <v>43378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3769,21 +3764,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>201146</v>
+        <v>201075</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3804,7 +3799,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3848,22 +3843,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2016-07-27</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2015-05-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2016-07-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2015-05-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3889,38 +3874,38 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60747030</t>
+          <t>https://artportalen.se/Sighting/55919018</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>78041334</v>
+        <v>72232452</v>
       </c>
       <c r="B27" t="n">
-        <v>56884</v>
+        <v>43258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208255</v>
+        <v>201129</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3935,10 +3920,14 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3985,22 +3974,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2019-05-23</t>
+          <t>2018-07-10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4027,38 +4016,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78041334</t>
+          <t>https://artportalen.se/Sighting/72232452</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>96043204</v>
+        <v>60747030</v>
       </c>
       <c r="B28" t="n">
-        <v>56876</v>
+        <v>43309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>208257</v>
+        <v>201146</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schneider, 1792)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4073,13 +4062,13 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4123,12 +4112,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-09-11</t>
+          <t>2016-07-27</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-09-11</t>
+          <t>2016-07-27</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4137,7 +4136,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4149,22 +4147,22 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96043204</t>
+          <t>https://artportalen.se/Sighting/60747030</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126246654</v>
+        <v>78041334</v>
       </c>
       <c r="B29" t="n">
-        <v>56905</v>
+        <v>56884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4172,21 +4170,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>208260</v>
+        <v>208255</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4205,7 +4203,11 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4247,12 +4249,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2019-05-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2019-05-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4273,22 +4285,22 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sven Halling, Ann Newsome</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126246654</t>
+          <t>https://artportalen.se/Sighting/78041334</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>16872227</v>
+        <v>96043204</v>
       </c>
       <c r="B30" t="n">
-        <v>99093</v>
+        <v>56876</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4296,31 +4308,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219797</v>
+        <v>208257</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Purpurknipprot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Epipactis atrorubens</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Besser</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>"Tegelbacken", Sm</t>
@@ -4357,12 +4387,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2009-07-30</t>
+          <t>2021-09-11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2009-07-30</t>
+          <t>2021-09-11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4371,6 +4401,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4382,22 +4413,22 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16872227</t>
+          <t>https://artportalen.se/Sighting/96043204</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126301886</v>
+        <v>126246654</v>
       </c>
       <c r="B31" t="n">
-        <v>99103</v>
+        <v>56905</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4405,39 +4436,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219799</v>
+        <v>208260</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>ex.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4479,22 +4511,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4521,16 +4543,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126301886</t>
+          <t>https://artportalen.se/Sighting/126246654</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>110386784</v>
+        <v>16872227</v>
       </c>
       <c r="B32" t="n">
-        <v>99156</v>
+        <v>99093</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4538,44 +4560,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219875</v>
+        <v>219797</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>blomning</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>"Tegelbacken", Sm</t>
@@ -4612,12 +4621,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
+          <t>2009-07-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-06-24</t>
+          <t>2009-07-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4626,7 +4635,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4644,53 +4652,53 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110386784</t>
+          <t>https://artportalen.se/Sighting/16872227</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>95858892</v>
+        <v>126301886</v>
       </c>
       <c r="B33" t="n">
-        <v>99118</v>
+        <v>99103</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>219799</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4735,12 +4743,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-09-01</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4767,62 +4785,74 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95858892</t>
+          <t>https://artportalen.se/Sighting/126301886</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96507865</v>
+        <v>110386784</v>
       </c>
       <c r="B34" t="n">
-        <v>99118</v>
+        <v>99156</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>219875</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>578722</v>
+        <v>578587</v>
       </c>
       <c r="R34" t="n">
-        <v>6410806</v>
+        <v>6410741</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4846,12 +4876,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4867,24 +4897,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96507865</t>
+          <t>https://artportalen.se/Sighting/110386784</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>96507964</v>
+        <v>95858892</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4914,7 +4944,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4922,22 +4952,30 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
+          <t>"Tegelbacken", Sm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>578689</v>
+        <v>578587</v>
       </c>
       <c r="R35" t="n">
-        <v>6410712</v>
+        <v>6410741</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4961,12 +4999,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4982,24 +5020,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96507964</t>
+          <t>https://artportalen.se/Sighting/95858892</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>102874367</v>
+        <v>96507865</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -5029,35 +5067,23 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>S 100 metersberget, Sm</t>
+          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>578754</v>
+        <v>578722</v>
       </c>
       <c r="R36" t="n">
-        <v>6410746</v>
+        <v>6410806</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5084,22 +5110,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:40</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:40</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5115,24 +5131,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102874367</t>
+          <t>https://artportalen.se/Sighting/96507865</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>102874540</v>
+        <v>96507964</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -5162,7 +5178,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5170,27 +5186,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>SSV 100 metersberget, Sm</t>
+          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>578695</v>
+        <v>578689</v>
       </c>
       <c r="R37" t="n">
-        <v>6410732</v>
+        <v>6410712</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5217,22 +5225,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>18:11</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2022-08-12</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>18:11</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5248,24 +5246,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102874540</t>
+          <t>https://artportalen.se/Sighting/96507964</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>111595448</v>
+        <v>102874367</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -5293,25 +5291,37 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Sm</t>
+          <t>S 100 metersberget, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>578729</v>
+        <v>578754</v>
       </c>
       <c r="R38" t="n">
-        <v>6410799</v>
+        <v>6410746</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5338,12 +5348,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5359,24 +5379,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111595448</t>
+          <t>https://artportalen.se/Sighting/102874367</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111595465</v>
+        <v>102874540</v>
       </c>
       <c r="B39" t="n">
         <v>99118</v>
@@ -5406,7 +5426,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5420,17 +5440,21 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Sm</t>
+          <t>SSV 100 metersberget, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>578746</v>
+        <v>578695</v>
       </c>
       <c r="R39" t="n">
-        <v>6410805</v>
+        <v>6410732</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5457,17 +5481,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5483,24 +5512,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111595465</t>
+          <t>https://artportalen.se/Sighting/102874540</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111595483</v>
+        <v>111595448</v>
       </c>
       <c r="B40" t="n">
         <v>99118</v>
@@ -5528,21 +5557,13 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -5551,10 +5572,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>578724</v>
+        <v>578729</v>
       </c>
       <c r="R40" t="n">
-        <v>6410783</v>
+        <v>6410799</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5589,11 +5610,6 @@
           <t>2023-08-20</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>6 blommor</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5618,63 +5634,67 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111595483</t>
+          <t>https://artportalen.se/Sighting/111595448</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96507995</v>
+        <v>111595465</v>
       </c>
       <c r="B41" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
+          <t>Svensgöl, Hult, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>578628</v>
+        <v>578746</v>
       </c>
       <c r="R41" t="n">
-        <v>6410775</v>
+        <v>6410805</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5701,12 +5721,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2021-10-06</t>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5727,49 +5752,49 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96507995</t>
+          <t>https://artportalen.se/Sighting/111595465</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>102425823</v>
+        <v>111595483</v>
       </c>
       <c r="B42" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5777,7 +5802,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
@@ -5786,10 +5815,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>578633</v>
+        <v>578724</v>
       </c>
       <c r="R42" t="n">
-        <v>6410766</v>
+        <v>6410783</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5816,12 +5845,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>6 blommor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5842,22 +5876,22 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102425823</t>
+          <t>https://artportalen.se/Sighting/111595483</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>96507688</v>
+        <v>96507995</v>
       </c>
       <c r="B43" t="n">
-        <v>97986</v>
+        <v>106244</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5865,21 +5899,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5901,10 +5935,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>578691</v>
+        <v>578628</v>
       </c>
       <c r="R43" t="n">
-        <v>6410795</v>
+        <v>6410775</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5963,16 +5997,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96507688</t>
+          <t>https://artportalen.se/Sighting/96507995</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>102425918</v>
+        <v>102425823</v>
       </c>
       <c r="B44" t="n">
-        <v>97986</v>
+        <v>106244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5980,31 +6014,31 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -6016,10 +6050,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>578697</v>
+        <v>578633</v>
       </c>
       <c r="R44" t="n">
-        <v>6410790</v>
+        <v>6410766</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6072,22 +6106,22 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Larsgunnar Nilsson, Sven Halling</t>
+          <t>Magnus Kasselstrand, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102425918</t>
+          <t>https://artportalen.se/Sighting/102425823</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117577625</v>
+        <v>96507688</v>
       </c>
       <c r="B45" t="n">
-        <v>104628</v>
+        <v>97986</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6095,16 +6129,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222412</v>
+        <v>221946</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -6119,29 +6153,25 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>"Tegelbacken", Sm</t>
+          <t>Svensgöl, Hult, Hallingeberg, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>578587</v>
+        <v>578691</v>
       </c>
       <c r="R45" t="n">
-        <v>6410741</v>
+        <v>6410795</v>
       </c>
       <c r="S45" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6165,22 +6195,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6196,27 +6216,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117577625</t>
+          <t>https://artportalen.se/Sighting/96507688</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>16878306</v>
+        <v>102425918</v>
       </c>
       <c r="B46" t="n">
-        <v>101326</v>
+        <v>97986</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6224,44 +6244,49 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>221946</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>"Tegelbacken", Sm</t>
+          <t>Svensgöl, Hult, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>578587</v>
+        <v>578697</v>
       </c>
       <c r="R46" t="n">
-        <v>6410741</v>
+        <v>6410790</v>
       </c>
       <c r="S46" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6285,12 +6310,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2011-06-01</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2011-06-01</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6299,22 +6324,261 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sven Halling</t>
+          <t>Magnus Kasselstrand, Larsgunnar Nilsson, Sven Halling</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102425918</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>117577625</v>
+      </c>
+      <c r="B47" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>"Tegelbacken", Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>578587</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6410741</v>
+      </c>
+      <c r="S47" t="n">
+        <v>100</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117577625</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>16878306</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>"Tegelbacken", Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>578587</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6410741</v>
+      </c>
+      <c r="S48" t="n">
+        <v>100</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Hallingeberg</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2011-06-01</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/16878306</t>
         </is>
@@ -6367,6 +6631,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
